--- a/115年醫師病房值班.xlsx
+++ b/115年醫師病房值班.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csw11\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB589EA-EBDF-436F-A415-9348D43DD808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32F3A27E-1EBF-4411-B092-C226DDE3ADEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="77">
   <si>
     <t>日期</t>
   </si>
@@ -204,10 +204,6 @@
   </si>
   <si>
     <t>陳建次</t>
-  </si>
-  <si>
-    <t>星期二1班
-星期五2班</t>
   </si>
   <si>
     <t>陳建次667856</t>
@@ -269,6 +265,18 @@
   </si>
   <si>
     <t>醫師姓名</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙數月份出現</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>單數月份出現</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>星期二、星期五</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -333,6 +341,7 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -423,7 +432,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -471,6 +480,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,14 +705,16 @@
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="7.796875" customWidth="1"/>
+    <col min="2" max="2" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="8" max="8" width="16.8984375" customWidth="1"/>
+    <col min="5" max="6" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>2</v>
@@ -833,8 +847,8 @@
         <v>3</v>
       </c>
       <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>54</v>
+      <c r="G6" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>36</v>
@@ -902,7 +916,7 @@
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -924,7 +938,7 @@
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H10" s="4"/>
     </row>
@@ -958,7 +972,7 @@
         <v>667856</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>27</v>
@@ -974,13 +988,13 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="2">
         <v>679007</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>27</v>
@@ -990,19 +1004,19 @@
       </c>
       <c r="F13" s="4"/>
       <c r="G13" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2">
         <v>678907</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>27</v>
@@ -1016,17 +1030,19 @@
       <c r="G14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="4" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" s="2">
         <v>678907</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>27</v>
@@ -1040,17 +1056,19 @@
       <c r="G15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H15" s="4"/>
+      <c r="H15" s="4" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="2">
         <v>679089</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>27</v>
@@ -1066,13 +1084,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2">
         <v>678910</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>27</v>
@@ -1103,7 +1121,7 @@
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
       <c r="H18" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1123,7 +1141,7 @@
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
       <c r="H19" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1143,7 +1161,7 @@
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1163,7 +1181,7 @@
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1352,84 +1370,84 @@
         <v>667856</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B13" s="1">
         <v>679007</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B14" s="1">
         <v>679087</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1">
         <v>679089</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1">
         <v>678907</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" s="1">
         <v>678907</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" s="1">
         <v>679089</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B19" s="1">
         <v>678910</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1584,7 +1602,7 @@
         <v>星期二</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D2" s="6"/>
       <c r="E2" s="7" t="str">
@@ -1872,7 +1890,7 @@
         <v>星期二</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="6"/>
       <c r="E16" s="7" t="str">
@@ -2095,7 +2113,7 @@
         <v>星期六</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="7" t="str">
